--- a/TEngine/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/__enums__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xx\NewText\TEngine\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B7B4367-F7F2-4317-AB46-1999D33DBE90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11E56055-D47B-4B85-8DB5-019338E8314E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="36000" yWindow="1020" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
   <si>
     <t>##var</t>
   </si>
@@ -164,10 +164,6 @@
   </si>
   <si>
     <t>英文</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>##</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -252,11 +248,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -569,13 +565,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -751,7 +747,7 @@
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C13" t="b">
@@ -760,27 +756,25 @@
       <c r="D13" t="b">
         <v>1</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="3" t="s">
         <v>43</v>
       </c>
       <c r="J13">
         <v>1</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="K13" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="H14" s="4" t="s">
+      <c r="A14" s="3"/>
+      <c r="H14" s="3" t="s">
         <v>41</v>
       </c>
       <c r="J14">
         <v>2</v>
       </c>
-      <c r="K14" s="4" t="s">
+      <c r="K14" s="3" t="s">
         <v>44</v>
       </c>
     </row>
